--- a/assets/constructions/examples/ctd_jse_hand_set.xlsx
+++ b/assets/constructions/examples/ctd_jse_hand_set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,11 +634,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M20x1 2621-1711/2621-1709.2 Р6М5К5 ГОСТ 3266-81</t>
+          <t>M30x2 2621-1947/2621-1945.2 Р6М5 ГОСТ 3266-81 с покрытием</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -653,12 +678,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMKN</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -673,20 +698,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ISO 2</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>M20x1</t>
+          <t>M30x2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -701,20 +726,20 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="T2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +748,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:14X11.2</t>
+          <t>DCON_X_DRVS:20x16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -735,17 +760,17 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.2</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Р6М5К5</t>
+          <t>Р6М5</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -777,7 +802,7 @@
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
@@ -791,13 +816,24 @@
       <c r="AO2" t="inlineStr">
         <is>
           <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M24x2 2621-1815/2621-1813.1 Р6М5К5 ГОСТ 3266-81 с покрытием</t>
+          <t>M20x0.75 2620-1704/2620-1702.2 Р6М5 ГОСТ 3266-81</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -812,12 +848,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -832,20 +868,20 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ISO 1</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>M24x2</t>
+          <t>M20x0.75</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -860,29 +896,29 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="R3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="T3" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:18X14</t>
+          <t>DCON_X_DRVS:14x11.2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -894,17 +930,17 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>11.2</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Р6М5К5</t>
+          <t>Р6М5</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -936,7 +972,7 @@
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
@@ -950,13 +986,24 @@
       <c r="AO3" t="inlineStr">
         <is>
           <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M12x1.25 2621-1504/2621-1502.1 Р6М5К5 ГОСТ 3266-81</t>
+          <t>M10x0.5 2621-2629/2621-2631.2 Р18 ГОСТ 3266-81 с покрытием</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -971,12 +1018,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -991,20 +1038,20 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ISO 1</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M12x1,25</t>
+          <t>M10x0.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1019,29 +1066,29 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="T4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:9X7.1</t>
+          <t>DCON_X_DRVS:8x6.3</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1053,17 +1100,17 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Р6М5К5</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1095,7 +1142,7 @@
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
@@ -1109,35 +1156,42 @@
       <c r="AO4" t="inlineStr">
         <is>
           <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M20x2 2621-1728/2621-1726.3 Р18 ГОСТ 3266-81</t>
+          <t>TAP M 5x0,5 SET- A 2 LH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
+          <t>VERGNANO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>КММП 3266</t>
+          <t>A2 LH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PNKS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>M60</t>
@@ -1150,20 +1204,20 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ISO 3</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>M20x2</t>
+          <t>M5x0.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1178,20 +1232,20 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1200,7 +1254,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:14X11.2</t>
+          <t>DCON_X_DRVS:6x4.9</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1208,11 +1262,9 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="X5" t="b">
-        <v>0</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>11.2</v>
+        <v>4.9</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1220,11 +1272,7 @@
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Р18</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>HSS</t>
@@ -1250,12 +1298,10 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>ГОСТ 3266-81</t>
-        </is>
-      </c>
-      <c r="AK5" t="n">
-        <v>17</v>
-      </c>
+          <t>DIN 2181</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>0</v>
@@ -1267,14 +1313,25 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+          <t>2022 / Vergnano-Thread-Mills</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M30x0.75 2620-1923/2620-1921.1 Р6М5К5 ГОСТ 3266-81</t>
+          <t>M24x3 2620-1821/2620-1819.2 Р6М5К5 ГОСТ 3266-81</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,25 +1361,25 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ISO 1</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>M30x0,75</t>
+          <t>M24x3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1337,20 +1394,20 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="R6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="T6" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1359,7 +1416,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:20X16</t>
+          <t>DCON_X_DRVS:18x14</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1371,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1413,7 +1470,7 @@
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
@@ -1427,6 +1484,17 @@
       <c r="AO6" t="inlineStr">
         <is>
           <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
